--- a/MONITOREO_LPI.xlsx
+++ b/MONITOREO_LPI.xlsx
@@ -15,25 +15,25 @@
   <definedNames>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">'PUBLICACIÓN EN AGENCIA'!$A$1:$F$1</definedName>
     <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">PUBLICADORES_X_DISTRITO!$A$1:$D$390</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_DAB2FA5A_2330_4B2B_95CE_704D8C5EF3DB_.wvu.FilterData">CONSOLIDADO!$AD$1:$AD$498</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_ECBBAA16_43BD_424C_842D_2A187E765D0E_.wvu.FilterData">CONSOLIDADO!$AB$1:$AB$498</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_BB0DFADC_3183_4274_A04F_0642C22F1D38_.wvu.FilterData">CONSOLIDADO!$AA$1:$AG$498</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_FF21AFF8_9B82_4578_9310_CDE6EBA51E08_.wvu.FilterData">CONSOLIDADO!$AD$1:$AD$498</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_30E67381_51E8_402B_9DB8_61A0371BCD8C_.wvu.FilterData">CONSOLIDADO!$AB$1:$AB$498</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_CA893DA8_5B0E_4972_8C00_4EC6B9C693A0_.wvu.FilterData">CONSOLIDADO!$A$1:$AT$499</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_B378EFA6_7EA4_411C_869D_46C1304B65D9_.wvu.FilterData">CONSOLIDADO!$AD$1:$AD$498</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_0F873B7A_6BD4_4702_BA68_B76B01E4BD4F_.wvu.FilterData">CONSOLIDADO!$AD$1:$AD$498</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_8BD43B63_69D3_4F91_BF43_CB085F005904_.wvu.FilterData">CONSOLIDADO!$AB$1:$AB$498</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_F6FDE535_E4E9_4FF6_9F90_1F6132628BE3_.wvu.FilterData">CONSOLIDADO!$AA$1:$AG$498</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_7F0C7FF4_1AE1_4615_8E1E_DCE4CBC97A99_.wvu.FilterData">CONSOLIDADO!$AD$1:$AD$498</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_5939E4FF_FD65_4B5E_9928_0EB4D081E823_.wvu.FilterData">CONSOLIDADO!$AB$1:$AB$498</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_728FA92A_2465_49A6_9590_F2B1E6FB6296_.wvu.FilterData">CONSOLIDADO!$AD$1:$AD$498</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_24EE773F_BB85_4B1E_975E_695BBA3E989D_.wvu.FilterData">CONSOLIDADO!$A$1:$AT$499</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_D624F9AA_B9E2_4855_B394_0FFA59AFBB54_.wvu.FilterData">CONSOLIDADO!$AD$1:$AD$498</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_9E23873C_5473_4F8F_857B_1FE74CA1DC49_.wvu.FilterData">CONSOLIDADO!$AD$1:$AD$498</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{CA893DA8-5B0E-4972-8C00-4EC6B9C693A0}" name="ARI"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{ECBBAA16-43BD-424C-842D-2A187E765D0E}" name="Filtro 4"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{30E67381-51E8-402B-9DB8-61A0371BCD8C}" name="Filtro 5"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{BB0DFADC-3183-4274-A04F-0642C22F1D38}" name="Filtro 6"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{B378EFA6-7EA4-411C-869D-46C1304B65D9}" name="Filtro 7"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{FF21AFF8-9B82-4578-9310-CDE6EBA51E08}" name="Filtro 1"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{DAB2FA5A-2330-4B2B-95CE-704D8C5EF3DB}" name="Filtro 2"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{0F873B7A-6BD4-4702-BA68-B76B01E4BD4F}" name="Filtro 3"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{24EE773F-BB85-4B1E-975E-695BBA3E989D}" name="ARI"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{5939E4FF-FD65-4B5E-9928-0EB4D081E823}" name="Filtro 4"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{8BD43B63-69D3-4F91-BF43-CB085F005904}" name="Filtro 5"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{F6FDE535-E4E9-4FF6-9F90-1F6132628BE3}" name="Filtro 6"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{D624F9AA-B9E2-4855-B394-0FFA59AFBB54}" name="Filtro 7"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{7F0C7FF4-1AE1-4615-8E1E-DCE4CBC97A99}" name="Filtro 1"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{9E23873C-5473-4F8F-857B-1FE74CA1DC49}" name="Filtro 2"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{728FA92A-2465-49A6-9590-F2B1E6FB6296}" name="Filtro 3"/>
   </customWorkbookViews>
 </workbook>
 </file>
@@ -42,44 +42,44 @@
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
     <author/>
-    <author>tc={07c59771-37fc-49bc-a7a8-a1d1a6bd2552}</author>
-    <author>tc={08f1c7dc-124f-4a67-b943-0f2cf1a4c788}</author>
-    <author>tc={0d6a1376-5153-4ca6-8e0c-9ab917ef7888}</author>
-    <author>tc={0e129886-f294-4683-a6c3-87162c0a8cd5}</author>
-    <author>tc={14eb2b87-9661-405a-838d-cb112b3888ef}</author>
-    <author>tc={15c05302-1b1d-4286-a352-8ae9f9764399}</author>
-    <author>tc={1931f1ea-71f2-48ee-9270-51614bb54239}</author>
-    <author>tc={1b76dea3-6159-4ffd-b9af-7b4d9c9e8544}</author>
-    <author>tc={2ddd7e2e-edab-4419-8e4b-a35738df7408}</author>
-    <author>tc={2fae3eb8-7585-41bf-b42b-cd671d15ffc7}</author>
-    <author>tc={32d5c6b8-df27-4ce7-9d3c-19fbbb282b7b}</author>
-    <author>tc={34953f52-5fce-4898-b6a0-1ad1fb3b05ee}</author>
-    <author>tc={382edeed-1632-4d4b-a620-c1713761bd32}</author>
-    <author>tc={3d4c3ead-b28a-4edb-8018-af8b424139ac}</author>
-    <author>tc={445104cf-767d-4084-a163-91b10debde3c}</author>
-    <author>tc={4a990ec1-dfd0-4a7c-8b08-e23a0a482fd8}</author>
-    <author>tc={4c55ddb9-d238-41cb-83e9-e5780c58a3a1}</author>
-    <author>tc={50215d91-8df9-4255-aac6-b92f88e13116}</author>
-    <author>tc={5798de6e-eaa0-48c3-aa50-eb374d960e7a}</author>
-    <author>tc={6f574208-3152-4595-a1e2-eed523336f4b}</author>
-    <author>tc={707dc141-8b38-43bd-bc65-a8ac2e8cbefb}</author>
-    <author>tc={75d14a69-8644-4972-a551-52db36f66306}</author>
-    <author>tc={7eaca773-2167-4e13-81ac-1fa18bbe5a14}</author>
-    <author>tc={8715455e-b687-4502-bdfe-90cb0c58b8bc}</author>
-    <author>tc={88446e53-7a01-45bd-a21b-1b44298fb75c}</author>
-    <author>tc={a52f636f-3058-4c5b-8449-29785320156f}</author>
-    <author>tc={bd452a35-f914-4b93-9d9b-0f604c59f299}</author>
-    <author>tc={c2672195-92f2-4356-a30f-16c5d5e89c11}</author>
-    <author>tc={c7f4f2e4-ef7d-4cc0-82c3-a21d9f803eca}</author>
-    <author>tc={d0837e90-1085-4c58-ac38-19e2b9e4968d}</author>
-    <author>tc={d33ab201-c519-4386-8007-8b91b7237c0d}</author>
-    <author>tc={d9b0f96d-fb58-4b8a-a37e-f6ada36dafbb}</author>
-    <author>tc={e02b3a87-330b-471c-8d2c-fb184762f9d2}</author>
-    <author>tc={e3675016-97e6-419e-9bfc-89306d5f48a9}</author>
-    <author>tc={e514e42e-893f-4b5b-854a-147fc3dcd618}</author>
-    <author>tc={e62ad4bb-056f-42c1-874c-f2911d893996}</author>
-    <author>tc={ea07f5bf-e689-415b-911d-a6f8c65cee92}</author>
-    <author>tc={f1a1b186-cdc5-49ed-b5ba-ee728e5e7695}</author>
+    <author>tc={04973876-dd2a-40b6-bbcd-6dafc4a56639}</author>
+    <author>tc={2bc49720-eedb-418a-964e-1d2a60a9f10d}</author>
+    <author>tc={2e7826a8-c469-41f9-892c-4799a2906b1c}</author>
+    <author>tc={32ae2a60-2780-438b-a54d-86a75d5e2eae}</author>
+    <author>tc={3b5eeb05-998b-41b5-a83e-fa0e389f2a97}</author>
+    <author>tc={3f0b752c-a55d-4172-8e46-5e2cd48067bd}</author>
+    <author>tc={544365b3-0c62-49a4-ab7b-0e451edd02b3}</author>
+    <author>tc={545508c1-306c-4bfb-90aa-3611abd25cf5}</author>
+    <author>tc={602557a6-cbbc-46b2-9fa3-75d0fb3a63b1}</author>
+    <author>tc={6a99b7ca-7e21-4787-8c2e-241598793e07}</author>
+    <author>tc={7011a9b8-f26d-4da7-8074-096a855e48df}</author>
+    <author>tc={70becc5c-f13c-4510-9e4f-c792fb6229bb}</author>
+    <author>tc={72effec1-50c0-439e-8f62-3c545ef8d884}</author>
+    <author>tc={774a1ae9-15cc-41a6-94f3-0ed433e53aa6}</author>
+    <author>tc={77d31b7c-bd61-4828-92d2-f35e755c9ab3}</author>
+    <author>tc={84c3627b-72ab-4561-a8ef-803f9abbbd87}</author>
+    <author>tc={860af8c1-e4ea-4c2a-89ab-f43f6908b7b3}</author>
+    <author>tc={87fddc94-18d4-4ab2-b97d-4d15978e5dd3}</author>
+    <author>tc={88530977-abc5-4c52-bec5-013c23d73b64}</author>
+    <author>tc={90be1b91-fd34-4964-a85f-38f75ccc1d4e}</author>
+    <author>tc={94d80daf-070f-4f76-ae3b-24b3301c1d15}</author>
+    <author>tc={9765d3cd-fce2-4851-b5c1-1f07dfcca95b}</author>
+    <author>tc={98023401-13bc-4dc6-a1d3-80c50fb5b6bb}</author>
+    <author>tc={9c1e3382-4101-43a1-9c09-1cddbad77bbe}</author>
+    <author>tc={9d9daefa-d70e-4f4f-b41c-1ff8e5689f3a}</author>
+    <author>tc={a8191836-0070-4c97-8504-f72497c27e5a}</author>
+    <author>tc={b216d371-e1de-4e05-809d-bc28efc86d81}</author>
+    <author>tc={b5120b3d-6b16-480d-955c-d318f358ba28}</author>
+    <author>tc={c6fd371e-fc93-489f-9606-abe5ee353479}</author>
+    <author>tc={ce1d4ace-26e5-46a3-9039-790ea6e9dc7a}</author>
+    <author>tc={ce62b951-59db-4cac-8001-f99bbe4794f0}</author>
+    <author>tc={d794f685-cdad-4364-9466-9657bf016fcc}</author>
+    <author>tc={daab62fd-3ea4-49d8-a2cc-0c4165d97e73}</author>
+    <author>tc={e1d94f36-2281-4d17-995e-50c134592ecd}</author>
+    <author>tc={e566166f-a8c5-47f5-891f-bcc1a81b19ab}</author>
+    <author>tc={e98fe937-17d1-4c06-b40d-9a5b5c1fb0de}</author>
+    <author>tc={f4ad5d3b-607e-42e9-8242-625446f8b26a}</author>
+    <author>tc={fc5cb7e4-1086-46c3-a702-f3a58f7186b4}</author>
   </authors>
   <commentList>
     <comment authorId="0" ref="Y137">
@@ -128,7 +128,178 @@
 Defunción: Recogerá viernes 2pm</t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{07c59771-37fc-49bc-a7a8-a1d1a6bd2552}" ref="W334">
+    <comment authorId="1" xr:uid="{04973876-dd2a-40b6-bbcd-6dafc4a56639}" ref="Y358">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	ME CONFIRMO X MENSAJE, PERO AUN NO ENVIA SUS FOTOS, SOLO EL DE COMISARIA
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{2bc49720-eedb-418a-964e-1d2a60a9f10d}" ref="Y375">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	No entrega comisaría porque está dirigido a Yurimaguas, que está a varias horas río arriba del distrito.
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{2e7826a8-c469-41f9-892c-4799a2906b1c}" ref="Y339">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	REVISAR LAS FOTOS PENDIENTES DE ENVIO OFICIOS MUNI Y REGISTRO CIVIL
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{32ae2a60-2780-438b-a54d-86a75d5e2eae}" ref="AC365">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	CASA MATERNA S/N
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{3b5eeb05-998b-41b5-a83e-fa0e389f2a97}" ref="Y366">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	No se entrega a comisaría en físico porque es la CPNC de yurimaguas, que está a cinco horas del distrito.
+</t>
+      </text>
+    </comment>
+    <comment authorId="6" xr:uid="{3f0b752c-a55d-4172-8e46-5e2cd48067bd}" ref="AC359">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	PVF - EL ESTRECHO (PNP)
+</t>
+      </text>
+    </comment>
+    <comment authorId="7" xr:uid="{544365b3-0c62-49a4-ab7b-0e451edd02b3}" ref="W336">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	EL 22 ENTREGA OFICIOS, LLEGO TARDE EL 21
+</t>
+      </text>
+    </comment>
+    <comment authorId="8" xr:uid="{545508c1-306c-4bfb-90aa-3611abd25cf5}" ref="AA365">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	JNE INDICO AL PUBLICADOR QUE PEGUE TODO EL PADRON
+</t>
+      </text>
+    </comment>
+    <comment authorId="9" xr:uid="{602557a6-cbbc-46b2-9fa3-75d0fb3a63b1}" ref="Y353">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Se entregó el oficio de la comisaria a la sub perfectura.
+</t>
+      </text>
+    </comment>
+    <comment authorId="10" xr:uid="{6a99b7ca-7e21-4787-8c2e-241598793e07}" ref="E355">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	RECOJE EN AGENCIA AMBOS KITS Y SE ENCONTRARA CON SU COMPAÑERO EN EL DISTRITO
+</t>
+      </text>
+    </comment>
+    <comment authorId="11" xr:uid="{7011a9b8-f26d-4da7-8074-096a855e48df}" ref="AF398">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	NO HAN PUESTO LOS DNI EN EL ACTA. VA A LEVANTAR OTRA ACTA EN LA TARDE
+</t>
+      </text>
+    </comment>
+    <comment authorId="12" xr:uid="{70becc5c-f13c-4510-9e4f-c792fb6229bb}" ref="E387">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	NUEVO INGRESO DE USUARIO
+</t>
+      </text>
+    </comment>
+    <comment authorId="13" xr:uid="{72effec1-50c0-439e-8f62-3c545ef8d884}" ref="U470">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Si
+</t>
+      </text>
+    </comment>
+    <comment authorId="14" xr:uid="{774a1ae9-15cc-41a6-94f3-0ed433e53aa6}" ref="Y350">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	OFICIO DE CATASTRO PRESENTARA MAÑANA, LA SECRETARIA ESTA ENFERMA Y LA MUNICIPALIDAD ESTA CERRADA
+</t>
+      </text>
+    </comment>
+    <comment authorId="15" xr:uid="{77d31b7c-bd61-4828-92d2-f35e755c9ab3}" ref="L493">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Si
+</t>
+      </text>
+    </comment>
+    <comment authorId="16" xr:uid="{84c3627b-72ab-4561-a8ef-803f9abbbd87}" ref="Y347">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	se entrego a la subperfectura
+</t>
+      </text>
+    </comment>
+    <comment authorId="17" xr:uid="{860af8c1-e4ea-4c2a-89ab-f43f6908b7b3}" ref="M346">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	SE ESTÁ VOLVIENDO A IMPRIMIR, LA RUTA ES FUERA DE PRESUPUESTO
+</t>
+      </text>
+    </comment>
+    <comment authorId="18" xr:uid="{87fddc94-18d4-4ab2-b97d-4d15978e5dd3}" ref="AC360">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	PVF - EL ESTRECHO (PNP)
+</t>
+      </text>
+    </comment>
+    <comment authorId="19" xr:uid="{88530977-abc5-4c52-bec5-013c23d73b64}" ref="AC353">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	FRONTIS HOSPEDAJE ALICE
+</t>
+      </text>
+    </comment>
+    <comment authorId="20" xr:uid="{90be1b91-fd34-4964-a85f-38f75ccc1d4e}" ref="W334">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -138,34 +309,25 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{08f1c7dc-124f-4a67-b943-0f2cf1a4c788}" ref="AC359">
+    <comment authorId="21" xr:uid="{94d80daf-070f-4f76-ae3b-24b3301c1d15}" ref="AC344">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	PVF - EL ESTRECHO (PNP)
+	OFICINA DESCENTRALIZADA DE EDUCACIÓN RURAL (ODER) JEBREOS
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{0d6a1376-5153-4ca6-8e0c-9ab917ef7888}" ref="AA365">
+    <comment authorId="22" xr:uid="{9765d3cd-fce2-4851-b5c1-1f07dfcca95b}" ref="AC339">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	JNE INDICO AL PUBLICADOR QUE PEGUE TODO EL PADRON
+	BARBERÍA EL PADRINO
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{0e129886-f294-4683-a6c3-87162c0a8cd5}" ref="M346">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	SE ESTÁ VOLVIENDO A IMPRIMIR, LA RUTA ES FUERA DE PRESUPUESTO
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{14eb2b87-9661-405a-838d-cb112b3888ef}" ref="G492">
+    <comment authorId="23" xr:uid="{98023401-13bc-4dc6-a1d3-80c50fb5b6bb}" ref="G492">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -174,16 +336,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="6" xr:uid="{15c05302-1b1d-4286-a352-8ae9f9764399}" ref="E176">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	OJO: que no publiquen en agencia
-</t>
-      </text>
-    </comment>
-    <comment authorId="7" xr:uid="{1931f1ea-71f2-48ee-9270-51614bb54239}" ref="Y369">
+    <comment authorId="24" xr:uid="{9c1e3382-4101-43a1-9c09-1cddbad77bbe}" ref="Y369">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -192,52 +345,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="8" xr:uid="{1b76dea3-6159-4ffd-b9af-7b4d9c9e8544}" ref="E387">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	NUEVO INGRESO DE USUARIO
-</t>
-      </text>
-    </comment>
-    <comment authorId="9" xr:uid="{2ddd7e2e-edab-4419-8e4b-a35738df7408}" ref="E355">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	RECOJE EN AGENCIA AMBOS KITS Y SE ENCONTRARA CON SU COMPAÑERO EN EL DISTRITO
-</t>
-      </text>
-    </comment>
-    <comment authorId="10" xr:uid="{2fae3eb8-7585-41bf-b42b-cd671d15ffc7}" ref="AC344">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	OFICINA DESCENTRALIZADA DE EDUCACIÓN RURAL (ODER) JEBREOS
-</t>
-      </text>
-    </comment>
-    <comment authorId="11" xr:uid="{32d5c6b8-df27-4ce7-9d3c-19fbbb282b7b}" ref="Y353">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	En el distrito no hay comisaría, se entregara a la sub perfectura
-</t>
-      </text>
-    </comment>
-    <comment authorId="12" xr:uid="{34953f52-5fce-4898-b6a0-1ad1fb3b05ee}" ref="Y366">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	No se entrega a comisaría en físico porque es la CPNC de yurimaguas, que está a cinco horas del distrito.
-</t>
-      </text>
-    </comment>
-    <comment authorId="13" xr:uid="{382edeed-1632-4d4b-a620-c1713761bd32}" ref="Y344">
+    <comment authorId="25" xr:uid="{9d9daefa-d70e-4f4f-b41c-1ff8e5689f3a}" ref="Y344">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -246,43 +354,34 @@
 </t>
       </text>
     </comment>
-    <comment authorId="14" xr:uid="{3d4c3ead-b28a-4edb-8018-af8b424139ac}" ref="Y350">
+    <comment authorId="26" xr:uid="{a8191836-0070-4c97-8504-f72497c27e5a}" ref="Y381">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	OFICIO DE CATASTRO PRESENTARA MAÑANA, LA SECRETARIA ESTA ENFERMA Y LA MUNICIPALIDAD ESTA CERRADA
+	NINGUNO, PORQUE PUBLICA EN AGENCIA
 </t>
       </text>
     </comment>
-    <comment authorId="15" xr:uid="{445104cf-767d-4084-a163-91b10debde3c}" ref="Y358">
+    <comment authorId="27" xr:uid="{b216d371-e1de-4e05-809d-bc28efc86d81}" ref="AC342">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	ME CONFIRMO X MENSAJE, PERO AUN NO ENVIA SUS FOTOS, SOLO EL DE COMISARIA
+	INSTITUTO CETPRO
 </t>
       </text>
     </comment>
-    <comment authorId="16" xr:uid="{4a990ec1-dfd0-4a7c-8b08-e23a0a482fd8}" ref="AF398">
+    <comment authorId="28" xr:uid="{b5120b3d-6b16-480d-955c-d318f358ba28}" ref="W175">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	NO HAN PUESTO LOS DNI EN EL ACTA. VA A LEVANTAR OTRA ACTA EN LA TARDE
+	NO HAY COMISARÍA
 </t>
       </text>
     </comment>
-    <comment authorId="17" xr:uid="{4c55ddb9-d238-41cb-83e9-e5780c58a3a1}" ref="AC365">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	CASA MATERNA S/N
-</t>
-      </text>
-    </comment>
-    <comment authorId="18" xr:uid="{50215d91-8df9-4255-aac6-b92f88e13116}" ref="AC334">
+    <comment authorId="29" xr:uid="{c6fd371e-fc93-489f-9606-abe5ee353479}" ref="AC334">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -291,25 +390,16 @@
 </t>
       </text>
     </comment>
-    <comment authorId="19" xr:uid="{5798de6e-eaa0-48c3-aa50-eb374d960e7a}" ref="U470">
+    <comment authorId="30" xr:uid="{ce1d4ace-26e5-46a3-9039-790ea6e9dc7a}" ref="X468">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Si
+	Hola
 </t>
       </text>
     </comment>
-    <comment authorId="20" xr:uid="{6f574208-3152-4595-a1e2-eed523336f4b}" ref="W175">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	NO HAY COMISARÍA
-</t>
-      </text>
-    </comment>
-    <comment authorId="21" xr:uid="{707dc141-8b38-43bd-bc65-a8ac2e8cbefb}" ref="Y357">
+    <comment authorId="31" xr:uid="{ce62b951-59db-4cac-8001-f99bbe4794f0}" ref="Y357">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -319,43 +409,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="22" xr:uid="{75d14a69-8644-4972-a551-52db36f66306}" ref="AC339">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	BARBERÍA EL PADRINO
-</t>
-      </text>
-    </comment>
-    <comment authorId="23" xr:uid="{7eaca773-2167-4e13-81ac-1fa18bbe5a14}" ref="L493">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Si
-</t>
-      </text>
-    </comment>
-    <comment authorId="24" xr:uid="{8715455e-b687-4502-bdfe-90cb0c58b8bc}" ref="W336">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	EL 22 ENTREGA OFICIOS, LLEGO TARDE EL 21
-</t>
-      </text>
-    </comment>
-    <comment authorId="25" xr:uid="{88446e53-7a01-45bd-a21b-1b44298fb75c}" ref="AC342">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	INSTITUTO CETPRO
-</t>
-      </text>
-    </comment>
-    <comment authorId="26" xr:uid="{a52f636f-3058-4c5b-8449-29785320156f}" ref="Y348">
+    <comment authorId="32" xr:uid="{d794f685-cdad-4364-9466-9657bf016fcc}" ref="Y348">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -364,16 +418,52 @@
 </t>
       </text>
     </comment>
-    <comment authorId="27" xr:uid="{bd452a35-f914-4b93-9d9b-0f604c59f299}" ref="AC353">
+    <comment authorId="33" xr:uid="{daab62fd-3ea4-49d8-a2cc-0c4165d97e73}" ref="Y353">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	FRONTIS HOSPEDAJE ALICE
+	En el distrito no hay comisaría, se entregara a la sub perfectura
 </t>
       </text>
     </comment>
-    <comment authorId="28" xr:uid="{c2672195-92f2-4356-a30f-16c5d5e89c11}" ref="AP384">
+    <comment authorId="34" xr:uid="{e1d94f36-2281-4d17-995e-50c134592ecd}" ref="AC336">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	TAMBO C.N. SANTA MARIA DE CAHUAPANAS
+</t>
+      </text>
+    </comment>
+    <comment authorId="35" xr:uid="{e566166f-a8c5-47f5-891f-bcc1a81b19ab}" ref="Y398">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	ES EL ANIVERSARIO DEL DISTRITO 22/04 Y NO LE HAN RECEPCIONADO DOCUMENTOS
+</t>
+      </text>
+    </comment>
+    <comment authorId="36" xr:uid="{e98fe937-17d1-4c06-b40d-9a5b5c1fb0de}" ref="E176">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	OJO: que no publiquen en agencia
+</t>
+      </text>
+    </comment>
+    <comment authorId="37" xr:uid="{f4ad5d3b-607e-42e9-8242-625446f8b26a}" ref="AC346">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	LOCAL MULTIUSO
+</t>
+      </text>
+    </comment>
+    <comment authorId="38" xr:uid="{fc5cb7e4-1086-46c3-a702-f3a58f7186b4}" ref="AP384">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -382,102 +472,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="29" xr:uid="{c7f4f2e4-ef7d-4cc0-82c3-a21d9f803eca}" ref="X468">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Hola
-</t>
-      </text>
-    </comment>
-    <comment authorId="30" xr:uid="{d0837e90-1085-4c58-ac38-19e2b9e4968d}" ref="AC360">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	PVF - EL ESTRECHO (PNP)
-</t>
-      </text>
-    </comment>
-    <comment authorId="31" xr:uid="{d33ab201-c519-4386-8007-8b91b7237c0d}" ref="Y375">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	No entrega comisaría porque está dirigido a Yurimaguas, que está a varias horas río arriba del distrito.
-</t>
-      </text>
-    </comment>
-    <comment authorId="32" xr:uid="{d9b0f96d-fb58-4b8a-a37e-f6ada36dafbb}" ref="Y398">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	ES EL ANIVERSARIO DEL DISTRITO 22/04 Y NO LE HAN RECEPCIONADO DOCUMENTOS
-</t>
-      </text>
-    </comment>
-    <comment authorId="33" xr:uid="{e02b3a87-330b-471c-8d2c-fb184762f9d2}" ref="Y339">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	REVISAR LAS FOTOS PENDIENTES DE ENVIO OFICIOS MUNI Y REGISTRO CIVIL
-</t>
-      </text>
-    </comment>
-    <comment authorId="34" xr:uid="{e3675016-97e6-419e-9bfc-89306d5f48a9}" ref="AC346">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	LOCAL MULTIUSO
-</t>
-      </text>
-    </comment>
-    <comment authorId="35" xr:uid="{e514e42e-893f-4b5b-854a-147fc3dcd618}" ref="Y347">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	se entrego a la subperfectura
-</t>
-      </text>
-    </comment>
-    <comment authorId="36" xr:uid="{e62ad4bb-056f-42c1-874c-f2911d893996}" ref="AC336">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	TAMBO C.N. SANTA MARIA DE CAHUAPANAS
-</t>
-      </text>
-    </comment>
-    <comment authorId="37" xr:uid="{ea07f5bf-e689-415b-911d-a6f8c65cee92}" ref="Y381">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	NINGUNO, PORQUE PUBLICA EN AGENCIA
-</t>
-      </text>
-    </comment>
-    <comment authorId="38" xr:uid="{f1a1b186-cdc5-49ed-b5ba-ee728e5e7695}" ref="Y353">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Se entregó el oficio de la comisaria a la sub perfectura.
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15031" uniqueCount="3251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15042" uniqueCount="3251">
   <si>
     <t>DATOS DEL PUBLICADOR</t>
   </si>
@@ -11853,11 +11853,11 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="María Chinchay" id="{92e02280-5a44-4767-ae0a-155e6d78d294}" providerId="google-sheets"/>
-  <x18tc:person displayName="Gremary Yahaira Lopez" id="{213698c8-8251-4c33-ba8c-01236d5be9ce}" providerId="google-sheets"/>
-  <x18tc:person displayName="Ruth Melanie Carbajal Escobar" id="{cc07aa18-8850-4e58-99f6-cb580302f6f3}" providerId="google-sheets"/>
-  <x18tc:person displayName="NAYELI JAZMIN LOPEZ PEÑA" id="{248013a6-088a-49d8-8c3b-ae2728fa4d58}" providerId="google-sheets"/>
-  <x18tc:person displayName="Mía Espejo" id="{741f7209-9fe7-4721-b0a0-eadcf387c62f}" providerId="google-sheets"/>
+  <x18tc:person displayName="María Chinchay" id="{b0043eec-3a00-4852-9330-491fa975da60}" providerId="google-sheets"/>
+  <x18tc:person displayName="Gremary Yahaira Lopez" id="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" providerId="google-sheets"/>
+  <x18tc:person displayName="Ruth Melanie Carbajal Escobar" id="{29d45a42-aaa6-4548-b673-e8164409403c}" providerId="google-sheets"/>
+  <x18tc:person displayName="NAYELI JAZMIN LOPEZ PEÑA" id="{cf50ed99-95c6-44db-b3cd-e334042112b1}" providerId="google-sheets"/>
+  <x18tc:person displayName="Mía Espejo" id="{a0492b4d-4655-4392-b056-a2e7df742e97}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -12173,120 +12173,120 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="X468" dT="2026-04-18T23:40:06.00" personId="{cc07aa18-8850-4e58-99f6-cb580302f6f3}" id="{c7f4f2e4-ef7d-4cc0-82c3-a21d9f803eca}" done="0">
+  <x18tc:threadedComment ref="X468" dT="2026-04-18T23:40:06.00" personId="{29d45a42-aaa6-4548-b673-e8164409403c}" id="{ce1d4ace-26e5-46a3-9039-790ea6e9dc7a}" done="0">
     <x18tc:text xml:space="preserve">Hola</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC365" dT="2026-04-22T16:22:09.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{4c55ddb9-d238-41cb-83e9-e5780c58a3a1}" done="0">
+  <x18tc:threadedComment ref="AC365" dT="2026-04-22T16:22:09.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{32ae2a60-2780-438b-a54d-86a75d5e2eae}" done="0">
     <x18tc:text xml:space="preserve">CASA MATERNA S/N</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="M346" dT="2026-04-16T17:48:27.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{0e129886-f294-4683-a6c3-87162c0a8cd5}" done="0">
+  <x18tc:threadedComment ref="M346" dT="2026-04-16T17:48:27.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{860af8c1-e4ea-4c2a-89ab-f43f6908b7b3}" done="0">
     <x18tc:text xml:space="preserve">SE ESTÁ VOLVIENDO A IMPRIMIR, LA RUTA ES FUERA DE PRESUPUESTO</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G492" dT="2026-04-18T23:42:07.00" personId="{cc07aa18-8850-4e58-99f6-cb580302f6f3}" id="{14eb2b87-9661-405a-838d-cb112b3888ef}" done="0">
+  <x18tc:threadedComment ref="G492" dT="2026-04-18T23:42:07.00" personId="{29d45a42-aaa6-4548-b673-e8164409403c}" id="{98023401-13bc-4dc6-a1d3-80c50fb5b6bb}" done="0">
     <x18tc:text xml:space="preserve">Nora</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC334" dT="2026-04-22T16:13:57.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{50215d91-8df9-4255-aac6-b92f88e13116}" done="0">
+  <x18tc:threadedComment ref="AC334" dT="2026-04-22T16:13:57.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{c6fd371e-fc93-489f-9606-abe5ee353479}" done="0">
     <x18tc:text xml:space="preserve">JUZGADO DE PAZ</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AP384" dT="2026-04-22T13:43:42.00" personId="{92e02280-5a44-4767-ae0a-155e6d78d294}" id="{c2672195-92f2-4356-a30f-16c5d5e89c11}" done="0">
+  <x18tc:threadedComment ref="AP384" dT="2026-04-22T13:43:42.00" personId="{b0043eec-3a00-4852-9330-491fa975da60}" id="{fc5cb7e4-1086-46c3-a702-f3a58f7186b4}" done="0">
     <x18tc:text xml:space="preserve">Se le indicó que le pida acompañamiento policial a la comisaría y que comunique inmediatamente si el alcalde va con tono amenazante</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="W175" dT="2026-04-21T20:32:48.00" personId="{248013a6-088a-49d8-8c3b-ae2728fa4d58}" id="{6f574208-3152-4595-a1e2-eed523336f4b}" done="1">
+  <x18tc:threadedComment ref="W175" dT="2026-04-21T20:32:48.00" personId="{cf50ed99-95c6-44db-b3cd-e334042112b1}" id="{b5120b3d-6b16-480d-955c-d318f358ba28}" done="1">
     <x18tc:text xml:space="preserve">NO HAY COMISARÍA</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="U470" dT="2026-04-18T23:39:27.00" personId="{cc07aa18-8850-4e58-99f6-cb580302f6f3}" id="{5798de6e-eaa0-48c3-aa50-eb374d960e7a}" done="0">
+  <x18tc:threadedComment ref="U470" dT="2026-04-18T23:39:27.00" personId="{29d45a42-aaa6-4548-b673-e8164409403c}" id="{72effec1-50c0-439e-8f62-3c545ef8d884}" done="0">
     <x18tc:text xml:space="preserve">Si</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y344" dT="2026-04-22T16:45:15.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{382edeed-1632-4d4b-a620-c1713761bd32}" done="0">
+  <x18tc:threadedComment ref="Y344" dT="2026-04-22T16:45:15.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{9d9daefa-d70e-4f4f-b41c-1ff8e5689f3a}" done="0">
     <x18tc:text xml:space="preserve">OFICIO DE COMISARIA SE PRESENTÓ AL JUEZ DE PAZ</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AF398" dT="2026-04-22T16:01:14.00" personId="{92e02280-5a44-4767-ae0a-155e6d78d294}" id="{4a990ec1-dfd0-4a7c-8b08-e23a0a482fd8}" done="1">
+  <x18tc:threadedComment ref="AF398" dT="2026-04-22T16:01:14.00" personId="{b0043eec-3a00-4852-9330-491fa975da60}" id="{7011a9b8-f26d-4da7-8074-096a855e48df}" done="1">
     <x18tc:text xml:space="preserve">NO HAN PUESTO LOS DNI EN EL ACTA. VA A LEVANTAR OTRA ACTA EN LA TARDE</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC336" dT="2026-04-22T17:45:47.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{e62ad4bb-056f-42c1-874c-f2911d893996}" done="0">
+  <x18tc:threadedComment ref="AC336" dT="2026-04-22T17:45:47.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{e1d94f36-2281-4d17-995e-50c134592ecd}" done="0">
     <x18tc:text xml:space="preserve">TAMBO C.N. SANTA MARIA DE CAHUAPANAS</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y366" dT="2026-04-21T18:15:11.00" personId="{92e02280-5a44-4767-ae0a-155e6d78d294}" id="{34953f52-5fce-4898-b6a0-1ad1fb3b05ee}" done="0">
+  <x18tc:threadedComment ref="Y366" dT="2026-04-21T18:15:11.00" personId="{b0043eec-3a00-4852-9330-491fa975da60}" id="{3b5eeb05-998b-41b5-a83e-fa0e389f2a97}" done="0">
     <x18tc:text xml:space="preserve">No se entrega a comisaría en físico porque es la CPNC de yurimaguas, que está a cinco horas del distrito.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC342" dT="2026-04-22T16:42:10.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{88446e53-7a01-45bd-a21b-1b44298fb75c}" done="0">
+  <x18tc:threadedComment ref="AC342" dT="2026-04-22T16:42:10.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{b216d371-e1de-4e05-809d-bc28efc86d81}" done="0">
     <x18tc:text xml:space="preserve">INSTITUTO CETPRO</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y398" dT="2026-04-22T16:00:41.00" personId="{92e02280-5a44-4767-ae0a-155e6d78d294}" id="{d9b0f96d-fb58-4b8a-a37e-f6ada36dafbb}" done="0">
+  <x18tc:threadedComment ref="Y398" dT="2026-04-22T16:00:41.00" personId="{b0043eec-3a00-4852-9330-491fa975da60}" id="{e566166f-a8c5-47f5-891f-bcc1a81b19ab}" done="0">
     <x18tc:text xml:space="preserve">ES EL ANIVERSARIO DEL DISTRITO 22/04 Y NO LE HAN RECEPCIONADO DOCUMENTOS</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC353" dT="2026-04-22T17:26:05.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{bd452a35-f914-4b93-9d9b-0f604c59f299}" done="0">
+  <x18tc:threadedComment ref="AC353" dT="2026-04-22T17:26:05.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{88530977-abc5-4c52-bec5-013c23d73b64}" done="0">
     <x18tc:text xml:space="preserve">FRONTIS HOSPEDAJE ALICE</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="L493" dT="2026-04-18T23:42:28.00" personId="{cc07aa18-8850-4e58-99f6-cb580302f6f3}" id="{7eaca773-2167-4e13-81ac-1fa18bbe5a14}" done="1">
+  <x18tc:threadedComment ref="L493" dT="2026-04-18T23:42:28.00" personId="{29d45a42-aaa6-4548-b673-e8164409403c}" id="{77d31b7c-bd61-4828-92d2-f35e755c9ab3}" done="1">
     <x18tc:text xml:space="preserve">Si</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC339" dT="2026-04-22T16:38:24.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{75d14a69-8644-4972-a551-52db36f66306}" done="0">
+  <x18tc:threadedComment ref="AC339" dT="2026-04-22T16:38:24.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{9765d3cd-fce2-4851-b5c1-1f07dfcca95b}" done="0">
     <x18tc:text xml:space="preserve">BARBERÍA EL PADRINO</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC360" dT="2026-04-22T17:24:17.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{d0837e90-1085-4c58-ac38-19e2b9e4968d}" done="0">
+  <x18tc:threadedComment ref="AC360" dT="2026-04-22T17:24:17.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{87fddc94-18d4-4ab2-b97d-4d15978e5dd3}" done="0">
     <x18tc:text xml:space="preserve">PVF - EL ESTRECHO (PNP)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y353" dT="2026-04-21T15:38:37.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{f1a1b186-cdc5-49ed-b5ba-ee728e5e7695}" done="0">
+  <x18tc:threadedComment ref="Y353" dT="2026-04-21T15:38:37.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{602557a6-cbbc-46b2-9fa3-75d0fb3a63b1}" done="0">
     <x18tc:text xml:space="preserve">Se entregó el oficio de la comisaria a la sub perfectura.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y348" dT="2026-04-21T17:04:47.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{a52f636f-3058-4c5b-8449-29785320156f}" done="0">
+  <x18tc:threadedComment ref="Y348" dT="2026-04-21T17:04:47.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{d794f685-cdad-4364-9466-9657bf016fcc}" done="0">
     <x18tc:text xml:space="preserve">se entrego a la subperfectura</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="W336" dT="2026-04-21T22:00:52.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{8715455e-b687-4502-bdfe-90cb0c58b8bc}" done="0">
+  <x18tc:threadedComment ref="W336" dT="2026-04-21T22:00:52.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{544365b3-0c62-49a4-ab7b-0e451edd02b3}" done="0">
     <x18tc:text xml:space="preserve">EL 22 ENTREGA OFICIOS, LLEGO TARDE EL 21</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y375" dT="2026-04-21T18:09:44.00" personId="{92e02280-5a44-4767-ae0a-155e6d78d294}" id="{d33ab201-c519-4386-8007-8b91b7237c0d}" done="1">
+  <x18tc:threadedComment ref="Y375" dT="2026-04-21T18:09:44.00" personId="{b0043eec-3a00-4852-9330-491fa975da60}" id="{2bc49720-eedb-418a-964e-1d2a60a9f10d}" done="1">
     <x18tc:text xml:space="preserve">No entrega comisaría porque está dirigido a Yurimaguas, que está a varias horas río arriba del distrito.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y369" dT="2026-04-21T17:20:48.00" personId="{92e02280-5a44-4767-ae0a-155e6d78d294}" id="{1931f1ea-71f2-48ee-9270-51614bb54239}" done="0">
+  <x18tc:threadedComment ref="Y369" dT="2026-04-21T17:20:48.00" personId="{b0043eec-3a00-4852-9330-491fa975da60}" id="{9c1e3382-4101-43a1-9c09-1cddbad77bbe}" done="0">
     <x18tc:text xml:space="preserve">No presenta a la Comisaría porque dice que está en un CP a tres horas del distrito.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y358" dT="2026-04-21T21:34:49.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{445104cf-767d-4084-a163-91b10debde3c}" done="0">
+  <x18tc:threadedComment ref="Y358" dT="2026-04-21T21:34:49.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{04973876-dd2a-40b6-bbcd-6dafc4a56639}" done="0">
     <x18tc:text xml:space="preserve">ME CONFIRMO X MENSAJE, PERO AUN NO ENVIA SUS FOTOS, SOLO EL DE COMISARIA</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y347" dT="2026-04-21T17:06:03.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{e514e42e-893f-4b5b-854a-147fc3dcd618}" done="0">
+  <x18tc:threadedComment ref="Y347" dT="2026-04-21T17:06:03.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{84c3627b-72ab-4561-a8ef-803f9abbbd87}" done="0">
     <x18tc:text xml:space="preserve">se entrego a la subperfectura</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y381" dT="2026-04-22T16:09:53.00" personId="{92e02280-5a44-4767-ae0a-155e6d78d294}" id="{ea07f5bf-e689-415b-911d-a6f8c65cee92}" done="0">
+  <x18tc:threadedComment ref="Y381" dT="2026-04-22T16:09:53.00" personId="{b0043eec-3a00-4852-9330-491fa975da60}" id="{a8191836-0070-4c97-8504-f72497c27e5a}" done="0">
     <x18tc:text xml:space="preserve">NINGUNO, PORQUE PUBLICA EN AGENCIA</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E355" dT="2026-04-16T17:21:10.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{2ddd7e2e-edab-4419-8e4b-a35738df7408}" done="0">
+  <x18tc:threadedComment ref="E355" dT="2026-04-16T17:21:10.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{6a99b7ca-7e21-4787-8c2e-241598793e07}" done="0">
     <x18tc:text xml:space="preserve">RECOJE EN AGENCIA AMBOS KITS Y SE ENCONTRARA CON SU COMPAÑERO EN EL DISTRITO</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AA365" dT="2026-04-23T01:07:09.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{0d6a1376-5153-4ca6-8e0c-9ab917ef7888}" done="0">
+  <x18tc:threadedComment ref="AA365" dT="2026-04-23T01:07:09.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{545508c1-306c-4bfb-90aa-3611abd25cf5}" done="0">
     <x18tc:text xml:space="preserve">JNE INDICO AL PUBLICADOR QUE PEGUE TODO EL PADRON</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC359" dT="2026-04-22T17:23:02.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{08f1c7dc-124f-4a67-b943-0f2cf1a4c788}" done="0">
+  <x18tc:threadedComment ref="AC359" dT="2026-04-22T17:23:02.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{3f0b752c-a55d-4172-8e46-5e2cd48067bd}" done="0">
     <x18tc:text xml:space="preserve">PVF - EL ESTRECHO (PNP)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y353" dT="2026-04-21T15:05:27.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{32d5c6b8-df27-4ce7-9d3c-19fbbb282b7b}" done="1">
+  <x18tc:threadedComment ref="Y353" dT="2026-04-21T15:05:27.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{daab62fd-3ea4-49d8-a2cc-0c4165d97e73}" done="1">
     <x18tc:text xml:space="preserve">En el distrito no hay comisaría, se entregara a la sub perfectura</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E387" dT="2026-04-18T22:00:16.00" personId="{741f7209-9fe7-4721-b0a0-eadcf387c62f}" id="{1b76dea3-6159-4ffd-b9af-7b4d9c9e8544}" done="0">
+  <x18tc:threadedComment ref="E387" dT="2026-04-18T22:00:16.00" personId="{a0492b4d-4655-4392-b056-a2e7df742e97}" id="{70becc5c-f13c-4510-9e4f-c792fb6229bb}" done="0">
     <x18tc:text xml:space="preserve">NUEVO INGRESO DE USUARIO</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y357" dT="2026-04-21T21:09:17.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{707dc141-8b38-43bd-bc65-a8ac2e8cbefb}" done="0">
+  <x18tc:threadedComment ref="Y357" dT="2026-04-21T21:09:17.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{ce62b951-59db-4cac-8001-f99bbe4794f0}" done="0">
     <x18tc:text xml:space="preserve">- VA A ENTREGAR LOS OTROS OFICIOS MALÑANA 22 /04/2026 TEMPRANO
 - EL DE AUTORIDADES NO HAY A QUIEN LO PRESENTE, NO SE ENCUENTRA EL SUBPERFECTO EN EL DISTRITO</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC346" dT="2026-04-22T17:13:39.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{e3675016-97e6-419e-9bfc-89306d5f48a9}" done="0">
+  <x18tc:threadedComment ref="AC346" dT="2026-04-22T17:13:39.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{f4ad5d3b-607e-42e9-8242-625446f8b26a}" done="0">
     <x18tc:text xml:space="preserve">LOCAL MULTIUSO</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="AC344" dT="2026-04-22T17:00:10.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{2fae3eb8-7585-41bf-b42b-cd671d15ffc7}" done="0">
+  <x18tc:threadedComment ref="AC344" dT="2026-04-22T17:00:10.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{94d80daf-070f-4f76-ae3b-24b3301c1d15}" done="0">
     <x18tc:text xml:space="preserve">OFICINA DESCENTRALIZADA DE EDUCACIÓN RURAL (ODER) JEBREOS</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y350" dT="2026-04-21T20:59:01.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{3d4c3ead-b28a-4edb-8018-af8b424139ac}" done="0">
+  <x18tc:threadedComment ref="Y350" dT="2026-04-21T20:59:01.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{774a1ae9-15cc-41a6-94f3-0ed433e53aa6}" done="0">
     <x18tc:text xml:space="preserve">OFICIO DE CATASTRO PRESENTARA MAÑANA, LA SECRETARIA ESTA ENFERMA Y LA MUNICIPALIDAD ESTA CERRADA</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="Y339" dT="2026-04-21T19:58:54.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{e02b3a87-330b-471c-8d2c-fb184762f9d2}" done="0">
+  <x18tc:threadedComment ref="Y339" dT="2026-04-21T19:58:54.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{2e7826a8-c469-41f9-892c-4799a2906b1c}" done="0">
     <x18tc:text xml:space="preserve">REVISAR LAS FOTOS PENDIENTES DE ENVIO OFICIOS MUNI Y REGISTRO CIVIL</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="W334" dT="2026-04-21T19:39:55.00" personId="{213698c8-8251-4c33-ba8c-01236d5be9ce}" id="{07c59771-37fc-49bc-a7a8-a1d1a6bd2552}" done="0">
+  <x18tc:threadedComment ref="W334" dT="2026-04-21T19:39:55.00" personId="{8b82fde3-d6d8-45f8-bd01-f08b14c656c9}" id="{90be1b91-fd34-4964-a85f-38f75ccc1d4e}" done="0">
     <x18tc:text xml:space="preserve">NO HAY SEÑAL, SOLO PARA LLAMADAS MOVISTAR...
 SE ESTA CONECTANDO AL WIFI DE LA MUNICIPALIDAD...</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E176" dT="2026-04-21T20:45:02.00" personId="{248013a6-088a-49d8-8c3b-ae2728fa4d58}" id="{15c05302-1b1d-4286-a352-8ae9f9764399}" done="1">
+  <x18tc:threadedComment ref="E176" dT="2026-04-21T20:45:02.00" personId="{cf50ed99-95c6-44db-b3cd-e334042112b1}" id="{e98fe937-17d1-4c06-b40d-9a5b5c1fb0de}" done="1">
     <x18tc:text xml:space="preserve">OJO: que no publiquen en agencia</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -12631,7 +12631,9 @@
       <c r="AH3" s="45">
         <v>10.0</v>
       </c>
-      <c r="AI3" s="45"/>
+      <c r="AI3" s="45">
+        <v>5.0</v>
+      </c>
       <c r="AJ3" s="45"/>
       <c r="AK3" s="45"/>
       <c r="AL3" s="45"/>
@@ -12743,13 +12745,15 @@
       <c r="AH4" s="45">
         <v>6.0</v>
       </c>
-      <c r="AI4" s="45"/>
+      <c r="AI4" s="45">
+        <v>8.0</v>
+      </c>
       <c r="AJ4" s="45"/>
       <c r="AK4" s="45"/>
       <c r="AL4" s="45"/>
       <c r="AM4" s="45"/>
       <c r="AN4" s="45">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="AO4" s="55"/>
       <c r="AP4" s="54"/>
@@ -12853,7 +12857,9 @@
       <c r="AH5" s="45">
         <v>5.0</v>
       </c>
-      <c r="AI5" s="45"/>
+      <c r="AI5" s="45">
+        <v>4.0</v>
+      </c>
       <c r="AJ5" s="45"/>
       <c r="AK5" s="45"/>
       <c r="AL5" s="45"/>
@@ -12965,7 +12971,9 @@
       <c r="AH6" s="45">
         <v>9.0</v>
       </c>
-      <c r="AI6" s="45"/>
+      <c r="AI6" s="45">
+        <v>16.0</v>
+      </c>
       <c r="AJ6" s="45"/>
       <c r="AK6" s="45"/>
       <c r="AL6" s="45"/>
@@ -13077,7 +13085,9 @@
       <c r="AH7" s="45">
         <v>5.0</v>
       </c>
-      <c r="AI7" s="45"/>
+      <c r="AI7" s="45">
+        <v>9.0</v>
+      </c>
       <c r="AJ7" s="45"/>
       <c r="AK7" s="45"/>
       <c r="AL7" s="45"/>
@@ -13297,7 +13307,9 @@
       <c r="AH9" s="45">
         <v>17.0</v>
       </c>
-      <c r="AI9" s="45"/>
+      <c r="AI9" s="45">
+        <v>9.0</v>
+      </c>
       <c r="AJ9" s="45"/>
       <c r="AK9" s="45"/>
       <c r="AL9" s="45"/>
@@ -13409,7 +13421,9 @@
       <c r="AH10" s="45">
         <v>85.0</v>
       </c>
-      <c r="AI10" s="45"/>
+      <c r="AI10" s="45">
+        <v>100.0</v>
+      </c>
       <c r="AJ10" s="45"/>
       <c r="AK10" s="45"/>
       <c r="AL10" s="45"/>
@@ -13635,7 +13649,9 @@
       <c r="AH12" s="45">
         <v>30.0</v>
       </c>
-      <c r="AI12" s="45"/>
+      <c r="AI12" s="45">
+        <v>50.0</v>
+      </c>
       <c r="AJ12" s="45"/>
       <c r="AK12" s="45"/>
       <c r="AL12" s="45"/>
@@ -13747,7 +13763,9 @@
       <c r="AH13" s="45">
         <v>13.0</v>
       </c>
-      <c r="AI13" s="45"/>
+      <c r="AI13" s="45">
+        <v>11.0</v>
+      </c>
       <c r="AJ13" s="45"/>
       <c r="AK13" s="45"/>
       <c r="AL13" s="45"/>
@@ -13857,7 +13875,9 @@
       <c r="AH14" s="45">
         <v>16.0</v>
       </c>
-      <c r="AI14" s="45"/>
+      <c r="AI14" s="45">
+        <v>12.0</v>
+      </c>
       <c r="AJ14" s="45"/>
       <c r="AK14" s="45"/>
       <c r="AL14" s="45"/>
@@ -13967,7 +13987,9 @@
       <c r="AH15" s="45">
         <v>16.0</v>
       </c>
-      <c r="AI15" s="45"/>
+      <c r="AI15" s="45">
+        <v>7.0</v>
+      </c>
       <c r="AJ15" s="45"/>
       <c r="AK15" s="45"/>
       <c r="AL15" s="45"/>
@@ -14275,7 +14297,9 @@
       <c r="AH18" s="45">
         <v>10.0</v>
       </c>
-      <c r="AI18" s="45"/>
+      <c r="AI18" s="45">
+        <v>9.0</v>
+      </c>
       <c r="AJ18" s="45"/>
       <c r="AK18" s="45"/>
       <c r="AL18" s="45"/>
@@ -14376,7 +14400,9 @@
         <v>67</v>
       </c>
       <c r="AG19" s="45"/>
-      <c r="AH19" s="45"/>
+      <c r="AH19" s="45">
+        <v>5.0</v>
+      </c>
       <c r="AI19" s="45"/>
       <c r="AJ19" s="45"/>
       <c r="AK19" s="45"/>
@@ -14597,7 +14623,9 @@
       <c r="AH21" s="45">
         <v>5.0</v>
       </c>
-      <c r="AI21" s="45"/>
+      <c r="AI21" s="45">
+        <v>0.0</v>
+      </c>
       <c r="AJ21" s="45"/>
       <c r="AK21" s="45"/>
       <c r="AL21" s="45"/>
@@ -14709,7 +14737,9 @@
       <c r="AH22" s="45">
         <v>20.0</v>
       </c>
-      <c r="AI22" s="45"/>
+      <c r="AI22" s="45">
+        <v>18.0</v>
+      </c>
       <c r="AJ22" s="45"/>
       <c r="AK22" s="45"/>
       <c r="AL22" s="45"/>
@@ -14821,7 +14851,9 @@
       <c r="AH23" s="45">
         <v>5.0</v>
       </c>
-      <c r="AI23" s="45"/>
+      <c r="AI23" s="45">
+        <v>6.0</v>
+      </c>
       <c r="AJ23" s="45"/>
       <c r="AK23" s="45"/>
       <c r="AL23" s="45"/>
@@ -14931,7 +14963,9 @@
       <c r="AH24" s="45">
         <v>8.0</v>
       </c>
-      <c r="AI24" s="45"/>
+      <c r="AI24" s="45">
+        <v>6.0</v>
+      </c>
       <c r="AJ24" s="45"/>
       <c r="AK24" s="45"/>
       <c r="AL24" s="45"/>
@@ -15041,7 +15075,9 @@
       <c r="AH25" s="45">
         <v>15.0</v>
       </c>
-      <c r="AI25" s="45"/>
+      <c r="AI25" s="45">
+        <v>5.0</v>
+      </c>
       <c r="AJ25" s="45"/>
       <c r="AK25" s="45"/>
       <c r="AL25" s="45"/>
@@ -15151,7 +15187,9 @@
       <c r="AH26" s="45">
         <v>5.0</v>
       </c>
-      <c r="AI26" s="45"/>
+      <c r="AI26" s="45">
+        <v>5.0</v>
+      </c>
       <c r="AJ26" s="45"/>
       <c r="AK26" s="45"/>
       <c r="AL26" s="45"/>
@@ -15261,7 +15299,9 @@
       <c r="AH27" s="45">
         <v>12.0</v>
       </c>
-      <c r="AI27" s="45"/>
+      <c r="AI27" s="45">
+        <v>7.0</v>
+      </c>
       <c r="AJ27" s="45"/>
       <c r="AK27" s="45"/>
       <c r="AL27" s="45"/>
@@ -15373,7 +15413,9 @@
       <c r="AH28" s="45">
         <v>50.0</v>
       </c>
-      <c r="AI28" s="45"/>
+      <c r="AI28" s="45">
+        <v>5.0</v>
+      </c>
       <c r="AJ28" s="45"/>
       <c r="AK28" s="45"/>
       <c r="AL28" s="45"/>
@@ -15699,7 +15741,9 @@
       <c r="AH31" s="45">
         <v>41.0</v>
       </c>
-      <c r="AI31" s="45"/>
+      <c r="AI31" s="45">
+        <v>18.0</v>
+      </c>
       <c r="AJ31" s="45"/>
       <c r="AK31" s="45"/>
       <c r="AL31" s="45"/>
@@ -15807,10 +15851,18 @@
       <c r="AH32" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="AI32" s="45"/>
-      <c r="AJ32" s="45"/>
-      <c r="AK32" s="45"/>
-      <c r="AL32" s="45"/>
+      <c r="AI32" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="AJ32" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="AK32" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="AL32" s="45" t="s">
+        <v>154</v>
+      </c>
       <c r="AM32" s="45"/>
       <c r="AN32" s="45" t="s">
         <v>154</v>
@@ -15908,13 +15960,21 @@
       <c r="AE33" s="54"/>
       <c r="AF33" s="45"/>
       <c r="AG33" s="45"/>
-      <c r="AH33" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI33" s="45"/>
-      <c r="AJ33" s="45"/>
-      <c r="AK33" s="45"/>
-      <c r="AL33" s="45"/>
+      <c r="AH33" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI33" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="AJ33" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="AK33" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="AL33" s="45" t="s">
+        <v>154</v>
+      </c>
       <c r="AM33" s="45"/>
       <c r="AN33" s="45" t="s">
         <v>154</v>
@@ -16017,7 +16077,9 @@
       <c r="AH34" s="45">
         <v>15.0</v>
       </c>
-      <c r="AI34" s="45"/>
+      <c r="AI34" s="45">
+        <v>6.0</v>
+      </c>
       <c r="AJ34" s="45"/>
       <c r="AK34" s="45"/>
       <c r="AL34" s="45"/>
@@ -17817,7 +17879,9 @@
       <c r="AH51" s="45">
         <v>48.0</v>
       </c>
-      <c r="AI51" s="69"/>
+      <c r="AI51" s="71">
+        <v>17.0</v>
+      </c>
       <c r="AJ51" s="45"/>
       <c r="AK51" s="45"/>
       <c r="AL51" s="45"/>
@@ -19840,10 +19904,12 @@
       <c r="AE70" s="89"/>
       <c r="AF70" s="84"/>
       <c r="AG70" s="84"/>
-      <c r="AH70" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI70" s="45"/>
+      <c r="AH70" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI70" s="45" t="s">
+        <v>154</v>
+      </c>
       <c r="AJ70" s="45"/>
       <c r="AK70" s="45"/>
       <c r="AL70" s="45"/>
@@ -19947,9 +20013,11 @@
       </c>
       <c r="AG71" s="84"/>
       <c r="AH71" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI71" s="45"/>
+        <v>15.0</v>
+      </c>
+      <c r="AI71" s="45">
+        <v>12.0</v>
+      </c>
       <c r="AJ71" s="45"/>
       <c r="AK71" s="45"/>
       <c r="AL71" s="45"/>
@@ -20051,9 +20119,11 @@
       </c>
       <c r="AG72" s="84"/>
       <c r="AH72" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI72" s="45"/>
+        <v>20.0</v>
+      </c>
+      <c r="AI72" s="45">
+        <v>25.0</v>
+      </c>
       <c r="AJ72" s="45"/>
       <c r="AK72" s="45"/>
       <c r="AL72" s="45"/>
@@ -20157,9 +20227,11 @@
       </c>
       <c r="AG73" s="84"/>
       <c r="AH73" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI73" s="45"/>
+        <v>15.0</v>
+      </c>
+      <c r="AI73" s="45">
+        <v>10.0</v>
+      </c>
       <c r="AJ73" s="45"/>
       <c r="AK73" s="45"/>
       <c r="AL73" s="45"/>
@@ -20265,9 +20337,11 @@
       </c>
       <c r="AG74" s="84"/>
       <c r="AH74" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI74" s="45"/>
+        <v>15.0</v>
+      </c>
+      <c r="AI74" s="45">
+        <v>11.0</v>
+      </c>
       <c r="AJ74" s="45"/>
       <c r="AK74" s="45"/>
       <c r="AL74" s="45"/>
@@ -20367,9 +20441,11 @@
       </c>
       <c r="AG75" s="84"/>
       <c r="AH75" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI75" s="45"/>
+        <v>50.0</v>
+      </c>
+      <c r="AI75" s="45">
+        <v>25.0</v>
+      </c>
       <c r="AJ75" s="45"/>
       <c r="AK75" s="45"/>
       <c r="AL75" s="45"/>
@@ -20469,9 +20545,11 @@
       </c>
       <c r="AG76" s="84"/>
       <c r="AH76" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI76" s="45"/>
+        <v>20.0</v>
+      </c>
+      <c r="AI76" s="45">
+        <v>22.0</v>
+      </c>
       <c r="AJ76" s="45"/>
       <c r="AK76" s="45"/>
       <c r="AL76" s="45"/>
@@ -20575,9 +20653,11 @@
       </c>
       <c r="AG77" s="84"/>
       <c r="AH77" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI77" s="45"/>
+        <v>16.0</v>
+      </c>
+      <c r="AI77" s="45">
+        <v>10.0</v>
+      </c>
       <c r="AJ77" s="45"/>
       <c r="AK77" s="45"/>
       <c r="AL77" s="45"/>
@@ -20681,9 +20761,11 @@
       </c>
       <c r="AG78" s="84"/>
       <c r="AH78" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI78" s="45"/>
+        <v>30.0</v>
+      </c>
+      <c r="AI78" s="45">
+        <v>21.0</v>
+      </c>
       <c r="AJ78" s="45"/>
       <c r="AK78" s="45"/>
       <c r="AL78" s="45"/>
@@ -20787,9 +20869,11 @@
       </c>
       <c r="AG79" s="84"/>
       <c r="AH79" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI79" s="45"/>
+        <v>25.0</v>
+      </c>
+      <c r="AI79" s="45">
+        <v>22.0</v>
+      </c>
       <c r="AJ79" s="45"/>
       <c r="AK79" s="45"/>
       <c r="AL79" s="45"/>
@@ -20895,9 +20979,11 @@
       </c>
       <c r="AG80" s="84"/>
       <c r="AH80" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI80" s="45"/>
+        <v>15.0</v>
+      </c>
+      <c r="AI80" s="45">
+        <v>10.0</v>
+      </c>
       <c r="AJ80" s="45"/>
       <c r="AK80" s="45"/>
       <c r="AL80" s="45"/>
@@ -20999,9 +21085,11 @@
       </c>
       <c r="AG81" s="84"/>
       <c r="AH81" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI81" s="45"/>
+        <v>60.0</v>
+      </c>
+      <c r="AI81" s="45">
+        <v>9.0</v>
+      </c>
       <c r="AJ81" s="45"/>
       <c r="AK81" s="45"/>
       <c r="AL81" s="45"/>
@@ -21107,9 +21195,11 @@
       </c>
       <c r="AG82" s="84"/>
       <c r="AH82" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI82" s="45"/>
+        <v>50.0</v>
+      </c>
+      <c r="AI82" s="45">
+        <v>24.0</v>
+      </c>
       <c r="AJ82" s="45"/>
       <c r="AK82" s="45"/>
       <c r="AL82" s="45"/>
@@ -21215,9 +21305,11 @@
       </c>
       <c r="AG83" s="84"/>
       <c r="AH83" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI83" s="45"/>
+        <v>22.0</v>
+      </c>
+      <c r="AI83" s="45">
+        <v>20.0</v>
+      </c>
       <c r="AJ83" s="45"/>
       <c r="AK83" s="45"/>
       <c r="AL83" s="45"/>
@@ -21321,9 +21413,11 @@
       </c>
       <c r="AG84" s="84"/>
       <c r="AH84" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI84" s="45"/>
+        <v>16.0</v>
+      </c>
+      <c r="AI84" s="45">
+        <v>6.0</v>
+      </c>
       <c r="AJ84" s="45"/>
       <c r="AK84" s="45"/>
       <c r="AL84" s="45"/>
@@ -21431,9 +21525,11 @@
       </c>
       <c r="AG85" s="84"/>
       <c r="AH85" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI85" s="45"/>
+        <v>30.0</v>
+      </c>
+      <c r="AI85" s="45">
+        <v>20.0</v>
+      </c>
       <c r="AJ85" s="45"/>
       <c r="AK85" s="45"/>
       <c r="AL85" s="45"/>
@@ -21539,9 +21635,11 @@
       </c>
       <c r="AG86" s="84"/>
       <c r="AH86" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI86" s="45"/>
+        <v>18.0</v>
+      </c>
+      <c r="AI86" s="45">
+        <v>5.0</v>
+      </c>
       <c r="AJ86" s="45"/>
       <c r="AK86" s="45"/>
       <c r="AL86" s="45"/>
@@ -21647,9 +21745,11 @@
       </c>
       <c r="AG87" s="84"/>
       <c r="AH87" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI87" s="45"/>
+        <v>25.0</v>
+      </c>
+      <c r="AI87" s="45">
+        <v>22.0</v>
+      </c>
       <c r="AJ87" s="45"/>
       <c r="AK87" s="45"/>
       <c r="AL87" s="45"/>
@@ -21755,9 +21855,11 @@
       </c>
       <c r="AG88" s="84"/>
       <c r="AH88" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI88" s="45"/>
+        <v>11.0</v>
+      </c>
+      <c r="AI88" s="45">
+        <v>7.0</v>
+      </c>
       <c r="AJ88" s="45"/>
       <c r="AK88" s="45"/>
       <c r="AL88" s="45"/>
@@ -21865,9 +21967,11 @@
       </c>
       <c r="AG89" s="84"/>
       <c r="AH89" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI89" s="45"/>
+        <v>20.0</v>
+      </c>
+      <c r="AI89" s="45">
+        <v>15.0</v>
+      </c>
       <c r="AJ89" s="45"/>
       <c r="AK89" s="45"/>
       <c r="AL89" s="45"/>
@@ -21973,9 +22077,11 @@
       </c>
       <c r="AG90" s="84"/>
       <c r="AH90" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI90" s="45"/>
+        <v>35.0</v>
+      </c>
+      <c r="AI90" s="45">
+        <v>25.0</v>
+      </c>
       <c r="AJ90" s="45"/>
       <c r="AK90" s="45"/>
       <c r="AL90" s="45"/>
@@ -22081,9 +22187,11 @@
       </c>
       <c r="AG91" s="84"/>
       <c r="AH91" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI91" s="45"/>
+        <v>24.0</v>
+      </c>
+      <c r="AI91" s="45">
+        <v>17.0</v>
+      </c>
       <c r="AJ91" s="45"/>
       <c r="AK91" s="45"/>
       <c r="AL91" s="45"/>
@@ -22187,9 +22295,11 @@
       </c>
       <c r="AG92" s="84"/>
       <c r="AH92" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI92" s="45"/>
+        <v>17.0</v>
+      </c>
+      <c r="AI92" s="45">
+        <v>12.0</v>
+      </c>
       <c r="AJ92" s="45"/>
       <c r="AK92" s="45"/>
       <c r="AL92" s="45"/>
@@ -22295,9 +22405,11 @@
       </c>
       <c r="AG93" s="84"/>
       <c r="AH93" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI93" s="45"/>
+        <v>22.0</v>
+      </c>
+      <c r="AI93" s="45">
+        <v>23.0</v>
+      </c>
       <c r="AJ93" s="45"/>
       <c r="AK93" s="45"/>
       <c r="AL93" s="45"/>
@@ -22401,9 +22513,11 @@
       </c>
       <c r="AG94" s="84"/>
       <c r="AH94" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI94" s="45"/>
+        <v>10.0</v>
+      </c>
+      <c r="AI94" s="45">
+        <v>8.0</v>
+      </c>
       <c r="AJ94" s="45"/>
       <c r="AK94" s="45"/>
       <c r="AL94" s="45"/>
@@ -22507,9 +22621,11 @@
       </c>
       <c r="AG95" s="84"/>
       <c r="AH95" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI95" s="45"/>
+        <v>18.0</v>
+      </c>
+      <c r="AI95" s="45">
+        <v>12.0</v>
+      </c>
       <c r="AJ95" s="45"/>
       <c r="AK95" s="45"/>
       <c r="AL95" s="45"/>
@@ -22611,9 +22727,11 @@
       </c>
       <c r="AG96" s="84"/>
       <c r="AH96" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI96" s="45"/>
+        <v>10.0</v>
+      </c>
+      <c r="AI96" s="45">
+        <v>11.0</v>
+      </c>
       <c r="AJ96" s="45"/>
       <c r="AK96" s="45"/>
       <c r="AL96" s="45"/>
@@ -22717,9 +22835,11 @@
       </c>
       <c r="AG97" s="84"/>
       <c r="AH97" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI97" s="45"/>
+        <v>12.0</v>
+      </c>
+      <c r="AI97" s="45">
+        <v>8.0</v>
+      </c>
       <c r="AJ97" s="45"/>
       <c r="AK97" s="45"/>
       <c r="AL97" s="45"/>
@@ -22825,9 +22945,11 @@
       </c>
       <c r="AG98" s="84"/>
       <c r="AH98" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI98" s="45"/>
+        <v>38.0</v>
+      </c>
+      <c r="AI98" s="45">
+        <v>33.0</v>
+      </c>
       <c r="AJ98" s="45"/>
       <c r="AK98" s="45"/>
       <c r="AL98" s="45"/>
@@ -22933,9 +23055,11 @@
       </c>
       <c r="AG99" s="84"/>
       <c r="AH99" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI99" s="45"/>
+        <v>35.0</v>
+      </c>
+      <c r="AI99" s="45">
+        <v>12.0</v>
+      </c>
       <c r="AJ99" s="45"/>
       <c r="AK99" s="45"/>
       <c r="AL99" s="45"/>
@@ -23039,9 +23163,11 @@
       </c>
       <c r="AG100" s="84"/>
       <c r="AH100" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI100" s="45"/>
+        <v>20.0</v>
+      </c>
+      <c r="AI100" s="45">
+        <v>12.0</v>
+      </c>
       <c r="AJ100" s="45"/>
       <c r="AK100" s="45"/>
       <c r="AL100" s="45"/>
@@ -23145,9 +23271,11 @@
       </c>
       <c r="AG101" s="84"/>
       <c r="AH101" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI101" s="45"/>
+        <v>18.0</v>
+      </c>
+      <c r="AI101" s="45">
+        <v>15.0</v>
+      </c>
       <c r="AJ101" s="45"/>
       <c r="AK101" s="45"/>
       <c r="AL101" s="45"/>
@@ -23253,9 +23381,11 @@
       </c>
       <c r="AG102" s="84"/>
       <c r="AH102" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="AI102" s="45"/>
+        <v>20.0</v>
+      </c>
+      <c r="AI102" s="45">
+        <v>17.0</v>
+      </c>
       <c r="AJ102" s="45"/>
       <c r="AK102" s="45"/>
       <c r="AL102" s="45"/>
@@ -65912,10 +66042,7 @@
       <c r="AE499" s="231"/>
       <c r="AF499" s="224"/>
       <c r="AG499" s="224"/>
-      <c r="AH499" s="229">
-        <f>SUM(AH3:AH498)</f>
-        <v>6632</v>
-      </c>
+      <c r="AH499" s="229"/>
       <c r="AI499" s="229"/>
       <c r="AJ499" s="229"/>
       <c r="AK499" s="229"/>
@@ -65931,7 +66058,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{CA893DA8-5B0E-4972-8C00-4EC6B9C693A0}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{24EE773F-BB85-4B1E-975E-695BBA3E989D}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$AT$499">
         <filterColumn colId="25">
           <filters blank="1">
@@ -65941,19 +66068,19 @@
         </filterColumn>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{DAB2FA5A-2330-4B2B-95CE-704D8C5EF3DB}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{9E23873C-5473-4F8F-857B-1FE74CA1DC49}" filter="1" showAutoFilter="1">
       <autoFilter ref="$AD$1:$AD$498"/>
     </customSheetView>
-    <customSheetView guid="{ECBBAA16-43BD-424C-842D-2A187E765D0E}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{5939E4FF-FD65-4B5E-9928-0EB4D081E823}" filter="1" showAutoFilter="1">
       <autoFilter ref="$AB$1:$AB$498"/>
     </customSheetView>
-    <customSheetView guid="{B378EFA6-7EA4-411C-869D-46C1304B65D9}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{D624F9AA-B9E2-4855-B394-0FFA59AFBB54}" filter="1" showAutoFilter="1">
       <autoFilter ref="$AD$1:$AD$498"/>
     </customSheetView>
-    <customSheetView guid="{0F873B7A-6BD4-4702-BA68-B76B01E4BD4F}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{728FA92A-2465-49A6-9590-F2B1E6FB6296}" filter="1" showAutoFilter="1">
       <autoFilter ref="$AD$1:$AD$498"/>
     </customSheetView>
-    <customSheetView guid="{30E67381-51E8-402B-9DB8-61A0371BCD8C}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{8BD43B63-69D3-4F91-BF43-CB085F005904}" filter="1" showAutoFilter="1">
       <autoFilter ref="$AB$1:$AB$498">
         <filterColumn colId="0">
           <filters>
@@ -65962,10 +66089,10 @@
         </filterColumn>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{BB0DFADC-3183-4274-A04F-0642C22F1D38}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{F6FDE535-E4E9-4FF6-9F90-1F6132628BE3}" filter="1" showAutoFilter="1">
       <autoFilter ref="$AA$1:$AG$498"/>
     </customSheetView>
-    <customSheetView guid="{FF21AFF8-9B82-4578-9310-CDE6EBA51E08}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{7F0C7FF4-1AE1-4615-8E1E-DCE4CBC97A99}" filter="1" showAutoFilter="1">
       <autoFilter ref="$AD$1:$AD$498">
         <filterColumn colId="0">
           <filters>
@@ -65982,8 +66109,8 @@
     <mergeCell ref="M1:U1"/>
     <mergeCell ref="W1:Y1"/>
     <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AN1"/>
     <mergeCell ref="AP1:AT1"/>
-    <mergeCell ref="AH1:AN1"/>
   </mergeCells>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J3:J499">
